--- a/experiment1/data_processing3/exp_data/07_no_outliers.xlsx
+++ b/experiment1/data_processing3/exp_data/07_no_outliers.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D241"/>
+  <dimension ref="A1:D247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -980,7 +980,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -993,12 +993,12 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>433.1428571428572</v>
+        <v>681</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1011,12 +1011,12 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>440</v>
+        <v>709.52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1029,12 +1029,12 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>406.84</v>
+        <v>723.4400000000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1047,12 +1047,12 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>462.0416666666667</v>
+        <v>693.25</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1065,12 +1065,12 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>440.5185185185185</v>
+        <v>710.0769230769231</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1083,12 +1083,12 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>432.962962962963</v>
+        <v>664.5769230769231</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1101,12 +1101,12 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>493.8571428571428</v>
+        <v>433.1428571428572</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1119,12 +1119,12 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>522.6296296296297</v>
+        <v>440</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1137,12 +1137,12 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>533.5666666666667</v>
+        <v>406.84</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1155,12 +1155,12 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>520.0645161290323</v>
+        <v>462.0416666666667</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1173,12 +1173,12 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>516.28</v>
+        <v>440.5185185185185</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -1191,12 +1191,12 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>528.375</v>
+        <v>432.962962962963</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -1209,12 +1209,12 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>477.962962962963</v>
+        <v>493.8571428571428</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -1227,12 +1227,12 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>533.8461538461538</v>
+        <v>522.6296296296297</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -1245,12 +1245,12 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>457.68</v>
+        <v>533.5666666666667</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -1263,12 +1263,12 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>484.8</v>
+        <v>520.0645161290323</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -1281,12 +1281,12 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>521.5454545454545</v>
+        <v>516.28</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1299,12 +1299,12 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>499.3703703703704</v>
+        <v>528.375</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1317,12 +1317,12 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>531.52</v>
+        <v>477.962962962963</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -1335,12 +1335,12 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>631.625</v>
+        <v>533.8461538461538</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -1353,12 +1353,12 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>534.2083333333334</v>
+        <v>457.68</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -1371,12 +1371,12 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>562.16</v>
+        <v>484.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -1389,12 +1389,12 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>651.16</v>
+        <v>521.5454545454545</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -1407,12 +1407,12 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>561.7307692307693</v>
+        <v>499.3703703703704</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -1425,12 +1425,12 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>526.72</v>
+        <v>540.4583333333334</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -1443,12 +1443,12 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>564.88</v>
+        <v>631.625</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -1461,12 +1461,12 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>522.9230769230769</v>
+        <v>534.2083333333334</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -1479,12 +1479,12 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>598.36</v>
+        <v>562.16</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -1497,12 +1497,12 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>568.76</v>
+        <v>651.16</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -1515,12 +1515,12 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>560.9642857142857</v>
+        <v>561.7307692307693</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -1533,12 +1533,12 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>548.5454545454545</v>
+        <v>526.72</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -1551,12 +1551,12 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>494.7</v>
+        <v>564.88</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -1569,12 +1569,12 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>527.8421052631579</v>
+        <v>522.9230769230769</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -1587,12 +1587,12 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>525.4814814814815</v>
+        <v>598.36</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -1605,12 +1605,12 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>536.4347826086956</v>
+        <v>568.76</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -1623,12 +1623,12 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>555.4193548387096</v>
+        <v>560.9642857142857</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -1641,12 +1641,12 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>612.16</v>
+        <v>548.5454545454545</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -1659,12 +1659,12 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>648.84</v>
+        <v>494.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -1677,12 +1677,12 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>558.6666666666666</v>
+        <v>527.8421052631579</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -1695,12 +1695,12 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>569.4782608695652</v>
+        <v>525.4814814814815</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -1713,12 +1713,12 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>672.2727272727273</v>
+        <v>536.4347826086956</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -1731,12 +1731,12 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>582.2272727272727</v>
+        <v>555.4193548387096</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -1749,12 +1749,12 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>381.5</v>
+        <v>612.16</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -1767,12 +1767,12 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>393.5925925925926</v>
+        <v>648.84</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -1785,12 +1785,12 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>378.92</v>
+        <v>558.6666666666666</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -1803,12 +1803,12 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>411.5925925925926</v>
+        <v>569.4782608695652</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -1821,12 +1821,12 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>420.5</v>
+        <v>672.2727272727273</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -1839,12 +1839,12 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>389.6538461538461</v>
+        <v>582.2272727272727</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -1857,12 +1857,12 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>503.6956521739131</v>
+        <v>381.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -1875,12 +1875,12 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>585.3076923076923</v>
+        <v>393.5925925925926</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -1893,12 +1893,12 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>507.2608695652174</v>
+        <v>378.92</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -1911,12 +1911,12 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>477.0869565217391</v>
+        <v>411.5925925925926</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -1929,12 +1929,12 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>560.6799999999999</v>
+        <v>420.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -1947,12 +1947,12 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>483.2</v>
+        <v>389.6538461538461</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -1965,12 +1965,12 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>384.5555555555555</v>
+        <v>503.6956521739131</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -1983,12 +1983,12 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>398.76</v>
+        <v>585.3076923076923</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -2001,12 +2001,12 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>413.0909090909091</v>
+        <v>507.2608695652174</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -2019,12 +2019,12 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>412.2352941176471</v>
+        <v>477.0869565217391</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -2037,12 +2037,12 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>410.3076923076923</v>
+        <v>560.6799999999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -2055,12 +2055,12 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>412.9032258064516</v>
+        <v>483.2</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -2073,12 +2073,12 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>467.3571428571428</v>
+        <v>384.5555555555555</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -2091,12 +2091,12 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>491.0384615384615</v>
+        <v>398.76</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -2109,12 +2109,12 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>465.6875</v>
+        <v>413.0909090909091</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -2127,12 +2127,12 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>459.625</v>
+        <v>412.2352941176471</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -2145,12 +2145,12 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>555.8846153846154</v>
+        <v>410.3076923076923</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -2163,12 +2163,12 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>539.9545454545455</v>
+        <v>412.9032258064516</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -2181,12 +2181,12 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>511.1538461538461</v>
+        <v>467.3571428571428</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -2199,12 +2199,12 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>484.8571428571428</v>
+        <v>491.0384615384615</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -2217,12 +2217,12 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>504.9166666666667</v>
+        <v>465.6875</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -2235,12 +2235,12 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>478.6086956521739</v>
+        <v>459.625</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -2253,12 +2253,12 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>476.9090909090909</v>
+        <v>555.8846153846154</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -2271,12 +2271,12 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>514.125</v>
+        <v>539.9545454545455</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -2289,12 +2289,12 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>473.0416666666667</v>
+        <v>511.1538461538461</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -2307,12 +2307,12 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>495.625</v>
+        <v>484.8571428571428</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -2325,12 +2325,12 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>493.44</v>
+        <v>504.9166666666667</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -2343,12 +2343,12 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>427.08</v>
+        <v>478.6086956521739</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -2361,12 +2361,12 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>471.1304347826087</v>
+        <v>476.9090909090909</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -2379,12 +2379,12 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>564.76</v>
+        <v>514.125</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -2397,12 +2397,12 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>528.5599999999999</v>
+        <v>473.0416666666667</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -2415,12 +2415,12 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>491</v>
+        <v>495.625</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -2433,12 +2433,12 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>578.3913043478261</v>
+        <v>493.44</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -2451,12 +2451,12 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>542.96</v>
+        <v>427.08</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -2469,12 +2469,12 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>506.28</v>
+        <v>471.1304347826087</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -2487,12 +2487,12 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>569.9642857142857</v>
+        <v>564.76</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -2505,12 +2505,12 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>386.0344827586207</v>
+        <v>528.5599999999999</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -2523,12 +2523,12 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>380.6428571428572</v>
+        <v>491</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -2541,12 +2541,12 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>402.4642857142857</v>
+        <v>578.3913043478261</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>394.9166666666667</v>
+        <v>542.96</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -2577,12 +2577,12 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>429.2592592592592</v>
+        <v>506.28</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -2595,12 +2595,12 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>395.9565217391304</v>
+        <v>569.9642857142857</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -2613,12 +2613,12 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>343.1904761904762</v>
+        <v>386.0344827586207</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -2631,12 +2631,12 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>339.9230769230769</v>
+        <v>380.6428571428572</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -2649,12 +2649,12 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>357.2592592592592</v>
+        <v>402.4642857142857</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -2667,12 +2667,12 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>374.16</v>
+        <v>394.9166666666667</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -2685,12 +2685,12 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>383.3478260869565</v>
+        <v>429.2592592592592</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -2703,12 +2703,12 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>343.6818181818182</v>
+        <v>395.9565217391304</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -2721,12 +2721,12 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>419</v>
+        <v>350.55</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -2739,12 +2739,12 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>422.9259259259259</v>
+        <v>339.9230769230769</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -2757,12 +2757,12 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>468.8846153846154</v>
+        <v>363.5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -2775,12 +2775,12 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>429.6956521739131</v>
+        <v>374.16</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -2793,12 +2793,12 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>479.375</v>
+        <v>371.1818181818182</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -2811,12 +2811,12 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>478.08</v>
+        <v>343.6818181818182</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -2829,12 +2829,12 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>478.0952380952381</v>
+        <v>419</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -2847,12 +2847,12 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>478.1739130434783</v>
+        <v>422.9259259259259</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -2865,12 +2865,12 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>445.5</v>
+        <v>468.8846153846154</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -2883,12 +2883,12 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>490.3103448275862</v>
+        <v>429.6956521739131</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -2901,12 +2901,12 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>469.4347826086956</v>
+        <v>479.375</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -2919,12 +2919,12 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>494.5</v>
+        <v>478.08</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -2937,12 +2937,12 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>659.6296296296297</v>
+        <v>478.0952380952381</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -2955,12 +2955,12 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>704.75</v>
+        <v>478.1739130434783</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -2973,12 +2973,12 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>656.4074074074074</v>
+        <v>445.5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -2991,12 +2991,12 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>651.04</v>
+        <v>490.3103448275862</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -3009,12 +3009,12 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>690.72</v>
+        <v>469.4347826086956</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -3027,12 +3027,12 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>631.08</v>
+        <v>494.5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -3045,12 +3045,12 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>532.2083333333334</v>
+        <v>659.6296296296297</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -3063,12 +3063,12 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>634.2692307692307</v>
+        <v>704.75</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -3081,12 +3081,12 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>533.2</v>
+        <v>656.4074074074074</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -3099,12 +3099,12 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>614.448275862069</v>
+        <v>651.04</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -3117,12 +3117,12 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>556.5185185185185</v>
+        <v>690.72</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -3135,12 +3135,12 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>495</v>
+        <v>631.08</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -3153,12 +3153,12 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>469.8260869565217</v>
+        <v>532.2083333333334</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -3171,12 +3171,12 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>591.0909090909091</v>
+        <v>634.2692307692307</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -3189,12 +3189,12 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>533.6666666666666</v>
+        <v>533.2</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -3207,12 +3207,12 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>502.7692307692308</v>
+        <v>614.448275862069</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -3225,12 +3225,12 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>617.5384615384615</v>
+        <v>556.5185185185185</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -3243,12 +3243,12 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>482.962962962963</v>
+        <v>495</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -3261,12 +3261,12 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>657.4400000000001</v>
+        <v>469.8260869565217</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -3279,12 +3279,12 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>572.304347826087</v>
+        <v>591.0909090909091</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -3297,12 +3297,12 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>701</v>
+        <v>533.6666666666666</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -3315,12 +3315,12 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>660.7857142857143</v>
+        <v>502.7692307692308</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -3333,12 +3333,12 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>555.1363636363636</v>
+        <v>617.5384615384615</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -3351,12 +3351,12 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>649.8846153846154</v>
+        <v>482.962962962963</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -3369,12 +3369,12 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>596.25</v>
+        <v>657.4400000000001</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -3387,12 +3387,12 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>569.8947368421053</v>
+        <v>572.304347826087</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -3405,12 +3405,12 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>603.5555555555555</v>
+        <v>701</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -3423,12 +3423,12 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>578.2727272727273</v>
+        <v>660.7857142857143</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -3441,12 +3441,12 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>581.6190476190476</v>
+        <v>555.1363636363636</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -3459,12 +3459,12 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>608.8695652173913</v>
+        <v>649.8846153846154</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -3477,12 +3477,12 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>399.3461538461539</v>
+        <v>596.25</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -3495,12 +3495,12 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>402.625</v>
+        <v>569.8947368421053</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -3513,12 +3513,12 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>389.28</v>
+        <v>603.5555555555555</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -3531,12 +3531,12 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>439.16</v>
+        <v>578.2727272727273</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -3549,12 +3549,12 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>483.375</v>
+        <v>581.6190476190476</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -3567,12 +3567,12 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>417.3846153846154</v>
+        <v>608.8695652173913</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -3585,12 +3585,12 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>480</v>
+        <v>399.3461538461539</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -3603,12 +3603,12 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>479.5925925925926</v>
+        <v>402.625</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -3621,12 +3621,12 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>484.9615384615385</v>
+        <v>389.28</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -3639,12 +3639,12 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>508.2692307692308</v>
+        <v>439.16</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -3657,12 +3657,12 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>492.8846153846154</v>
+        <v>483.375</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -3675,12 +3675,12 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>483.7692307692308</v>
+        <v>417.3846153846154</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -3693,12 +3693,12 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>532.3333333333334</v>
+        <v>480</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -3711,12 +3711,12 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>599.6521739130435</v>
+        <v>479.5925925925926</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -3729,12 +3729,12 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>541.5833333333334</v>
+        <v>484.9615384615385</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -3747,12 +3747,12 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>537</v>
+        <v>508.2692307692308</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -3765,12 +3765,12 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>616.7727272727273</v>
+        <v>492.8846153846154</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -3783,12 +3783,12 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>579.1153846153846</v>
+        <v>483.7692307692308</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -3801,12 +3801,12 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>422.2916666666667</v>
+        <v>532.3333333333334</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -3819,12 +3819,12 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>475.0740740740741</v>
+        <v>599.6521739130435</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -3837,12 +3837,12 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>471.8260869565217</v>
+        <v>541.5833333333334</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -3855,12 +3855,12 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>460.551724137931</v>
+        <v>537</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -3873,12 +3873,12 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>475.5769230769231</v>
+        <v>616.7727272727273</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -3891,12 +3891,12 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>462</v>
+        <v>579.1153846153846</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -3909,12 +3909,12 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>492.1111111111111</v>
+        <v>422.2916666666667</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -3927,12 +3927,12 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>475.4814814814815</v>
+        <v>475.0740740740741</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -3945,12 +3945,12 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>452.1481481481482</v>
+        <v>471.8260869565217</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -3963,12 +3963,12 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>501.0740740740741</v>
+        <v>460.551724137931</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -3981,12 +3981,12 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>502.12</v>
+        <v>475.5769230769231</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -3999,12 +3999,12 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>515.6296296296297</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -4017,12 +4017,12 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>569.7142857142857</v>
+        <v>492.1111111111111</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -4035,12 +4035,12 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>587.12</v>
+        <v>475.4814814814815</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -4053,12 +4053,12 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>594.3333333333334</v>
+        <v>452.1481481481482</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -4071,12 +4071,12 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>599.4736842105264</v>
+        <v>501.0740740740741</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -4089,12 +4089,12 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>655.2916666666666</v>
+        <v>502.12</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -4107,12 +4107,12 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>553</v>
+        <v>515.6296296296297</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -4125,12 +4125,12 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>399.88</v>
+        <v>569.7142857142857</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -4143,12 +4143,12 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>434</v>
+        <v>587.12</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -4161,12 +4161,12 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>401.2903225806452</v>
+        <v>594.3333333333334</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -4179,12 +4179,12 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>434</v>
+        <v>599.4736842105264</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -4197,12 +4197,12 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>433.5925925925926</v>
+        <v>655.2916666666666</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -4215,12 +4215,12 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>427.6190476190476</v>
+        <v>553</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -4233,12 +4233,12 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>628.1034482758621</v>
+        <v>399.88</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -4251,12 +4251,12 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>811.7037037037037</v>
+        <v>434</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -4269,12 +4269,12 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>621.8571428571429</v>
+        <v>401.2903225806452</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -4287,12 +4287,12 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>627.3636363636364</v>
+        <v>434</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -4305,12 +4305,12 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>723.7391304347826</v>
+        <v>433.5925925925926</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -4323,12 +4323,12 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>655.1935483870968</v>
+        <v>427.6190476190476</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -4341,12 +4341,12 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>423.9285714285714</v>
+        <v>628.1034482758621</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -4359,12 +4359,12 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>462</v>
+        <v>811.7037037037037</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -4377,12 +4377,12 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>443.125</v>
+        <v>621.8571428571429</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -4395,12 +4395,12 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>420.5833333333333</v>
+        <v>627.3636363636364</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -4413,12 +4413,12 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>490.6923076923077</v>
+        <v>723.7391304347826</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -4431,12 +4431,12 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>432.5555555555555</v>
+        <v>655.1935483870968</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -4449,12 +4449,12 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>425.3913043478261</v>
+        <v>423.9285714285714</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -4467,12 +4467,12 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>488.75</v>
+        <v>462</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -4485,12 +4485,12 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>458.7407407407408</v>
+        <v>443.125</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -4503,12 +4503,12 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>455.1538461538461</v>
+        <v>420.5833333333333</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -4521,12 +4521,12 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>448.4230769230769</v>
+        <v>490.6923076923077</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
@@ -4539,12 +4539,12 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>442.6666666666667</v>
+        <v>432.5555555555555</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B230" t="inlineStr">
         <is>
@@ -4557,12 +4557,12 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>599.1666666666666</v>
+        <v>436.0454545454546</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B231" t="inlineStr">
         <is>
@@ -4575,12 +4575,12 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>640.2962962962963</v>
+        <v>488.75</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B232" t="inlineStr">
         <is>
@@ -4593,12 +4593,12 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>654.76</v>
+        <v>458.7407407407408</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B233" t="inlineStr">
         <is>
@@ -4611,12 +4611,12 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>627.3571428571429</v>
+        <v>455.1538461538461</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
@@ -4629,12 +4629,12 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>627.8461538461538</v>
+        <v>448.4230769230769</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
@@ -4647,12 +4647,12 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>594.4400000000001</v>
+        <v>442.6666666666667</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
@@ -4665,12 +4665,12 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>641.2105263157895</v>
+        <v>599.1666666666666</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
@@ -4683,12 +4683,12 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>550.28</v>
+        <v>640.2962962962963</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B238" t="inlineStr">
         <is>
@@ -4701,12 +4701,12 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>586.84</v>
+        <v>654.76</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B239" t="inlineStr">
         <is>
@@ -4719,12 +4719,12 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>656.1</v>
+        <v>627.3571428571429</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B240" t="inlineStr">
         <is>
@@ -4737,24 +4737,132 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>625.08</v>
+        <v>627.8461538461538</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
+        <v>54</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>incongruent</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>inconsistent</t>
+        </is>
+      </c>
+      <c r="D241" t="n">
+        <v>594.4400000000001</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
         <v>55</v>
       </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>incongruent</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
-        <is>
-          <t>inconsistent</t>
-        </is>
-      </c>
-      <c r="D241" t="n">
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>congruent</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>consistent</t>
+        </is>
+      </c>
+      <c r="D242" t="n">
+        <v>641.2105263157895</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>55</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>congruent</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D243" t="n">
+        <v>550.28</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>55</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>congruent</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>inconsistent</t>
+        </is>
+      </c>
+      <c r="D244" t="n">
+        <v>586.84</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>55</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>incongruent</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>consistent</t>
+        </is>
+      </c>
+      <c r="D245" t="n">
+        <v>656.1</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>55</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>incongruent</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>control</t>
+        </is>
+      </c>
+      <c r="D246" t="n">
+        <v>625.08</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>55</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>incongruent</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>inconsistent</t>
+        </is>
+      </c>
+      <c r="D247" t="n">
         <v>634.1428571428571</v>
       </c>
     </row>
